--- a/public/templates-files/tm-ticket-template.xlsx
+++ b/public/templates-files/tm-ticket-template.xlsx
@@ -1609,7 +1609,7 @@
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8&amp;K8B93A1Free template by BuildWorkPro · buildworkpro.com/templates&amp;C&amp;8&amp;K8B93A1T&amp;M Ticket&amp;R&amp;8&amp;K8B93A1Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8&amp;K8B93A1Free template by BuildWorkPro · buildworkpro.com/templates&amp;C&amp;8&amp;K8B93A1T&amp;&amp;M Ticket&amp;R&amp;8&amp;K8B93A1Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2112,7 +2112,7 @@
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;8&amp;K8B93A1Free template by BuildWorkPro · buildworkpro.com/templates&amp;C&amp;8&amp;K8B93A1T&amp;M Log&amp;R&amp;8&amp;K8B93A1Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8&amp;K8B93A1Free template by BuildWorkPro · buildworkpro.com/templates&amp;C&amp;8&amp;K8B93A1T&amp;&amp;M Log&amp;R&amp;8&amp;K8B93A1Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
